--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -1701,7 +1701,7 @@
         <v>69000</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1824,7 +1824,7 @@
         <v>69000</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1836,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J22">
         <v>0</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>business_date</t>
   </si>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>Katamaa Diroo</t>
+  </si>
+  <si>
+    <t>Girmaa Masqalaa</t>
   </si>
 </sst>
 </file>
@@ -943,10 +946,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -2056,6 +2062,47 @@
         <v>51464</v>
       </c>
     </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B28">
+        <v>1027</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28">
+        <v>69000</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>138000</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>2000</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>business_date</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>Girmaa Masqalaa</t>
+  </si>
+  <si>
+    <t>Waktole Gutata</t>
   </si>
 </sst>
 </file>
@@ -946,13 +949,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="39.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -2103,6 +2115,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>46221</v>
+      </c>
+      <c r="B29">
+        <v>1028</v>
+      </c>
+      <c r="C29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29">
+        <v>69000</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>138000</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>2000</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -953,18 +953,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="39.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1596,7 +1584,7 @@
         <v>69000</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>98000</v>
       </c>
       <c r="F16">
         <v>0</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\general\EGSA2026_27_plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Waltana\Desktop from C\general\EGSA2026_27_plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -953,6 +953,12 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1054,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G3">
         <v>138000</v>
@@ -1382,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G11">
         <v>138000</v>
@@ -1710,7 +1716,7 @@
         <v>73000</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G19">
         <v>138000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -19,45 +19,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
   <si>
-    <t>ID</t>
+    <t>id</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>EGSA2026_27_first_half_year_plan</t>
-  </si>
-  <si>
-    <t>EGSA2026_27_first_half_year_achievement</t>
-  </si>
-  <si>
     <t>EGSA2026_27_monthly_payment</t>
   </si>
   <si>
-    <t>EGSA2026_27_second_half_year_plan</t>
-  </si>
-  <si>
-    <t>EGSA2026_27_second_half_year_achievement</t>
-  </si>
-  <si>
-    <t>fee_charge</t>
-  </si>
-  <si>
-    <t>volentary_saving</t>
-  </si>
-  <si>
-    <t>Benefit_gain</t>
-  </si>
-  <si>
-    <t>Expenditure</t>
-  </si>
-  <si>
     <t>End_2026_achievement</t>
+  </si>
+  <si>
+    <t>EGSA2027_Half_Year_plan</t>
+  </si>
+  <si>
+    <t>EGSA2027_Half_Year_achievement</t>
+  </si>
+  <si>
+    <t>NULL</t>
   </si>
   <si>
     <t>Geetu Bekela</t>
@@ -949,19 +934,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -983,1170 +962,648 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>45854</v>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
       </c>
       <c r="B2">
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>88893</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G2">
-        <v>138000</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>88893</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>45795</v>
+        <v>46223</v>
       </c>
       <c r="B3">
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>69000</v>
+        <v>1000</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="F3">
-        <v>1000</v>
+        <v>69000</v>
       </c>
       <c r="G3">
-        <v>138000</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>151000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>45814</v>
+        <v>46223</v>
       </c>
       <c r="B4">
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>69000</v>
+        <v>1000</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G4">
-        <v>138000</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>151000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>45795</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
       </c>
       <c r="B5">
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>84553</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G5">
-        <v>138000</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>84553</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>45854</v>
+        <v>46228</v>
       </c>
       <c r="B6">
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>69000</v>
+        <v>1000</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>61406</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G6">
-        <v>138000</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>61406</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>45795</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
       </c>
       <c r="B7">
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G7">
-        <v>138000</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>151000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>45795</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>7</v>
       </c>
       <c r="B8">
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>59067</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G8">
-        <v>138000</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>59067</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>45795</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>7</v>
       </c>
       <c r="B9">
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D9">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>145036</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G9">
-        <v>138000</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>145036</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>45818</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
       </c>
       <c r="B10">
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>61406</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G10">
-        <v>138000</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>61406</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>45844</v>
+        <v>46223</v>
       </c>
       <c r="B11">
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D11">
-        <v>69000</v>
+        <v>1000</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="F11">
-        <v>1000</v>
+        <v>69000</v>
       </c>
       <c r="G11">
-        <v>138000</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>151000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>45935</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>7</v>
       </c>
       <c r="B12">
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D12">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>59067</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G12">
-        <v>138000</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>59067</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>45849</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>7</v>
       </c>
       <c r="B13">
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D13">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>153500</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G13">
-        <v>138000</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>153500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>45862</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>7</v>
       </c>
       <c r="B14">
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D14">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>101759</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G14">
-        <v>138000</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>101759</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>45846</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>7</v>
       </c>
       <c r="B15">
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D15">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>102928</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G15">
-        <v>138000</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>102928</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>45977</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>7</v>
       </c>
       <c r="B16">
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D16">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E16">
+        <v>184553</v>
+      </c>
+      <c r="F16">
+        <v>69000</v>
+      </c>
+      <c r="G16">
         <v>98000</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>138000</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>184553</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>46000</v>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>7</v>
       </c>
       <c r="B17">
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D17">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>54973</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G17">
-        <v>138000</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>54973</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>46004</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>7</v>
       </c>
       <c r="B18">
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D18">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>73327</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G18">
-        <v>138000</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>73327</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>46164</v>
+        <v>46223</v>
       </c>
       <c r="B19">
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D19">
-        <v>69000</v>
+        <v>1000</v>
       </c>
       <c r="E19">
+        <v>49125</v>
+      </c>
+      <c r="F19">
+        <v>69000</v>
+      </c>
+      <c r="G19">
         <v>73000</v>
       </c>
-      <c r="F19">
-        <v>1000</v>
-      </c>
-      <c r="G19">
-        <v>138000</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>49125</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>46209</v>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>7</v>
       </c>
       <c r="B20">
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D20">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G20">
-        <v>138000</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>2000</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>46039</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>7</v>
       </c>
       <c r="B21">
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D21">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>51464</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G21">
-        <v>138000</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>51464</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>46210</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>7</v>
       </c>
       <c r="B22">
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D22">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>69000</v>
+      </c>
+      <c r="G22">
         <v>13000</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>138000</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>2000</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>46039</v>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>7</v>
       </c>
       <c r="B23">
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D23">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>65500</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G23">
-        <v>138000</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>65500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>46052</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>7</v>
       </c>
       <c r="B24">
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D24">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>53803</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G24">
-        <v>138000</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>53803</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>46057</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>7</v>
       </c>
       <c r="B25">
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D25">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>199000</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G25">
-        <v>138000</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>199000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>46170</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>7</v>
       </c>
       <c r="B26">
         <v>1025</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D26">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>49125</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G26">
-        <v>138000</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>49125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>46170</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>7</v>
       </c>
       <c r="B27">
         <v>1026</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D27">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>51464</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G27">
-        <v>138000</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>51464</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>46213</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>7</v>
       </c>
       <c r="B28">
         <v>1027</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D28">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G28">
-        <v>138000</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>2000</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>46221</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>7</v>
       </c>
       <c r="B29">
         <v>1028</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D29">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="G29">
-        <v>138000</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>2000</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
         <v>0</v>
       </c>
     </row>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -938,6 +938,12 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -19,30 +19,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>business_date</t>
   </si>
   <si>
-    <t>id</t>
+    <t>ID</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
+    <t>EGSA2026_27_first_half_year_plan</t>
+  </si>
+  <si>
+    <t>EGSA2026_27_first_half_year_achievement</t>
+  </si>
+  <si>
     <t>EGSA2026_27_monthly_payment</t>
   </si>
   <si>
+    <t>EGSA2026_27_second_half_year_plan</t>
+  </si>
+  <si>
+    <t>EGSA2026_27_second_half_year_achievement</t>
+  </si>
+  <si>
+    <t>fee_charge</t>
+  </si>
+  <si>
+    <t>volentary_saving</t>
+  </si>
+  <si>
+    <t>Benefit_gain</t>
+  </si>
+  <si>
+    <t>Expenditure</t>
+  </si>
+  <si>
     <t>End_2026_achievement</t>
-  </si>
-  <si>
-    <t>EGSA2027_Half_Year_plan</t>
-  </si>
-  <si>
-    <t>EGSA2027_Half_Year_achievement</t>
-  </si>
-  <si>
-    <t>NULL</t>
   </si>
   <si>
     <t>Geetu Bekela</t>
@@ -934,19 +949,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -968,648 +977,1170 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>45854</v>
       </c>
       <c r="B2">
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>138000</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
         <v>88893</v>
       </c>
-      <c r="F2">
-        <v>69000</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>46223</v>
+        <v>45795</v>
       </c>
       <c r="B3">
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D3">
+        <v>69000</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>1000</v>
       </c>
-      <c r="E3">
+      <c r="G3">
+        <v>138000</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>151000</v>
       </c>
-      <c r="F3">
-        <v>69000</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>46223</v>
+        <v>45814</v>
       </c>
       <c r="B4">
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D4">
+        <v>69000</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>1000</v>
       </c>
-      <c r="E4">
+      <c r="G4">
+        <v>138000</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>151000</v>
       </c>
-      <c r="F4">
-        <v>69000</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>45795</v>
       </c>
       <c r="B5">
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>138000</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
         <v>84553</v>
       </c>
-      <c r="F5">
-        <v>69000</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>46228</v>
+        <v>45854</v>
       </c>
       <c r="B6">
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D6">
+        <v>69000</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>1000</v>
       </c>
-      <c r="E6">
+      <c r="G6">
+        <v>138000</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
         <v>61406</v>
       </c>
-      <c r="F6">
-        <v>69000</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>7</v>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>45795</v>
       </c>
       <c r="B7">
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>138000</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
         <v>151000</v>
       </c>
-      <c r="F7">
-        <v>69000</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>7</v>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>45795</v>
       </c>
       <c r="B8">
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>138000</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
         <v>59067</v>
       </c>
-      <c r="F8">
-        <v>69000</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>45795</v>
       </c>
       <c r="B9">
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>138000</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
         <v>145036</v>
       </c>
-      <c r="F9">
-        <v>69000</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>7</v>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>45818</v>
       </c>
       <c r="B10">
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>138000</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
         <v>61406</v>
       </c>
-      <c r="F10">
-        <v>69000</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>46223</v>
+        <v>45844</v>
       </c>
       <c r="B11">
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D11">
+        <v>69000</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>1000</v>
       </c>
-      <c r="E11">
+      <c r="G11">
+        <v>138000</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>151000</v>
       </c>
-      <c r="F11">
-        <v>69000</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>7</v>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>45935</v>
       </c>
       <c r="B12">
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>138000</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>59067</v>
       </c>
-      <c r="F12">
-        <v>69000</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>7</v>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>45849</v>
       </c>
       <c r="B13">
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>138000</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>153500</v>
       </c>
-      <c r="F13">
-        <v>69000</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>7</v>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>45862</v>
       </c>
       <c r="B14">
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>138000</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>101759</v>
       </c>
-      <c r="F14">
-        <v>69000</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>7</v>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>45846</v>
       </c>
       <c r="B15">
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>138000</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>102928</v>
       </c>
-      <c r="F15">
-        <v>69000</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>7</v>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>45977</v>
       </c>
       <c r="B16">
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E16">
+        <v>98000</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>138000</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>184553</v>
       </c>
-      <c r="F16">
-        <v>69000</v>
-      </c>
-      <c r="G16">
-        <v>98000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>7</v>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>46000</v>
       </c>
       <c r="B17">
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>138000</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>54973</v>
       </c>
-      <c r="F17">
-        <v>69000</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>7</v>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>46004</v>
       </c>
       <c r="B18">
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>138000</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
         <v>73327</v>
       </c>
-      <c r="F18">
-        <v>69000</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>46223</v>
+        <v>46164</v>
       </c>
       <c r="B19">
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D19">
+        <v>69000</v>
+      </c>
+      <c r="E19">
+        <v>73000</v>
+      </c>
+      <c r="F19">
         <v>1000</v>
       </c>
-      <c r="E19">
+      <c r="G19">
+        <v>138000</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
         <v>49125</v>
       </c>
-      <c r="F19">
-        <v>69000</v>
-      </c>
-      <c r="G19">
-        <v>73000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>7</v>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>46209</v>
       </c>
       <c r="B20">
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>7</v>
+        <v>138000</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>2000</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>46039</v>
       </c>
       <c r="B21">
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>138000</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <v>51464</v>
       </c>
-      <c r="F21">
-        <v>69000</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>7</v>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>46210</v>
       </c>
       <c r="B22">
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="F22">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>7</v>
+        <v>138000</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>2000</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>46039</v>
       </c>
       <c r="B23">
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>138000</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>65500</v>
       </c>
-      <c r="F23">
-        <v>69000</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>7</v>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>46052</v>
       </c>
       <c r="B24">
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>138000</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>53803</v>
       </c>
-      <c r="F24">
-        <v>69000</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>7</v>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>46057</v>
       </c>
       <c r="B25">
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>138000</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>199000</v>
       </c>
-      <c r="F25">
-        <v>69000</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>7</v>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>46170</v>
       </c>
       <c r="B26">
         <v>1025</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>138000</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
         <v>49125</v>
       </c>
-      <c r="F26">
-        <v>69000</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>7</v>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>46170</v>
       </c>
       <c r="B27">
         <v>1026</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>138000</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>51464</v>
       </c>
-      <c r="F27">
-        <v>69000</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>7</v>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>46213</v>
       </c>
       <c r="B28">
         <v>1027</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>7</v>
+        <v>138000</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>2000</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>46221</v>
       </c>
       <c r="B29">
         <v>1028</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="G29">
+        <v>138000</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>2000</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
         <v>0</v>
       </c>
     </row>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -953,6 +953,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1505,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G14">
         <v>138000</v>
@@ -1830,10 +1831,10 @@
         <v>69000</v>
       </c>
       <c r="E22">
-        <v>13000</v>
+        <v>27000</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G22">
         <v>138000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -953,7 +953,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1014,7 +1013,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G2">
         <v>138000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G7">
         <v>138000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -953,6 +953,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1300,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G9">
         <v>138000</v>
@@ -1423,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G12">
         <v>138000</v>
@@ -1997,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G26">
         <v>138000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -953,7 +953,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1875,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G23">
         <v>138000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G13">
         <v>138000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G18">
         <v>138000</v>
@@ -2076,10 +2076,10 @@
         <v>69000</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G28">
         <v>138000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -2094,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L28">
         <v>0</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1546,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G15">
         <v>138000</v>
@@ -2117,10 +2117,10 @@
         <v>69000</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G29">
         <v>138000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -953,6 +953,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1092,7 +1094,7 @@
         <v>69000</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F4">
         <v>1000</v>
@@ -1174,7 +1176,7 @@
         <v>69000</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F6">
         <v>1000</v>
@@ -1215,7 +1217,7 @@
         <v>69000</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F7">
         <v>1000</v>
@@ -1297,7 +1299,7 @@
         <v>69000</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F9">
         <v>1000</v>
@@ -1379,7 +1381,7 @@
         <v>69000</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F11">
         <v>1000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -953,8 +953,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1586,10 +1585,10 @@
         <v>69000</v>
       </c>
       <c r="E16">
-        <v>98000</v>
+        <v>99000</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G16">
         <v>138000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -953,7 +953,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1260,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G8">
         <v>138000</v>
@@ -1316,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1439,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="L12">
         <v>0</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G10">
         <v>138000</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G20">
         <v>138000</v>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G21">
         <v>138000</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G27">
         <v>138000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G24">
         <v>138000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G25">
         <v>138000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>business_date</t>
   </si>
@@ -142,6 +142,12 @@
   </si>
   <si>
     <t>Waktole Gutata</t>
+  </si>
+  <si>
+    <t>Tarreessaa Wadajoo</t>
+  </si>
+  <si>
+    <t>Baay`isaa Kabbadaa</t>
   </si>
 </sst>
 </file>
@@ -949,10 +955,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -2144,6 +2153,88 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B30">
+        <v>1029</v>
+      </c>
+      <c r="C30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30">
+        <v>69000</v>
+      </c>
+      <c r="E30">
+        <v>1000</v>
+      </c>
+      <c r="F30">
+        <v>1000</v>
+      </c>
+      <c r="G30">
+        <v>138000</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>46271</v>
+      </c>
+      <c r="B31">
+        <v>1030</v>
+      </c>
+      <c r="C31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31">
+        <v>69000</v>
+      </c>
+      <c r="E31">
+        <v>1000</v>
+      </c>
+      <c r="F31">
+        <v>1000</v>
+      </c>
+      <c r="G31">
+        <v>138000</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -1470,7 +1470,7 @@
         <v>69000</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>98000</v>
       </c>
       <c r="F13">
         <v>1000</v>
@@ -1634,7 +1634,7 @@
         <v>69000</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="F17">
         <v>0</v>
